--- a/samples/예시데이터_구매현황(25.07~26.02).xlsx
+++ b/samples/예시데이터_구매현황(25.07~26.02).xlsx
@@ -555,7 +555,7 @@
         <v>300</v>
       </c>
       <c r="M3">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="N3" t="str">
         <v>EA</v>
@@ -564,7 +564,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>30000</v>
+        <v>16200</v>
       </c>
       <c r="Q3" t="str">
         <v>본사</v>
@@ -623,7 +623,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>30000</v>
+        <v>16200</v>
       </c>
       <c r="Q4" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>200</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="N5" t="str">
         <v>EA</v>
@@ -682,7 +682,7 @@
         <v/>
       </c>
       <c r="P5">
-        <v>20000</v>
+        <v>10800</v>
       </c>
       <c r="Q5" t="str">
         <v>본사</v>
@@ -741,7 +741,7 @@
         <v/>
       </c>
       <c r="P6">
-        <v>20000</v>
+        <v>10800</v>
       </c>
       <c r="Q6" t="str">
         <v/>
@@ -791,7 +791,7 @@
         <v>400</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="N7" t="str">
         <v>EA</v>
@@ -800,7 +800,7 @@
         <v/>
       </c>
       <c r="P7">
-        <v>40000</v>
+        <v>21600</v>
       </c>
       <c r="Q7" t="str">
         <v>본사</v>
@@ -859,7 +859,7 @@
         <v/>
       </c>
       <c r="P8">
-        <v>40000</v>
+        <v>21600</v>
       </c>
       <c r="Q8" t="str">
         <v/>
@@ -909,7 +909,7 @@
         <v>1200</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="N9" t="str">
         <v>EA</v>
@@ -918,7 +918,7 @@
         <v/>
       </c>
       <c r="P9">
-        <v>120000</v>
+        <v>64800</v>
       </c>
       <c r="Q9" t="str">
         <v>본사</v>
@@ -977,7 +977,7 @@
         <v/>
       </c>
       <c r="P10">
-        <v>120000</v>
+        <v>64800</v>
       </c>
       <c r="Q10" t="str">
         <v/>
@@ -1027,7 +1027,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>4680</v>
       </c>
       <c r="N11" t="str">
         <v>EA</v>
@@ -1036,7 +1036,7 @@
         <v/>
       </c>
       <c r="P11">
-        <v>10000</v>
+        <v>468000</v>
       </c>
       <c r="Q11" t="str">
         <v>본사</v>
@@ -1095,7 +1095,7 @@
         <v/>
       </c>
       <c r="P12">
-        <v>10000</v>
+        <v>468000</v>
       </c>
       <c r="Q12" t="str">
         <v/>
@@ -1145,7 +1145,7 @@
         <v>4000</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="N13" t="str">
         <v>EA</v>
@@ -1154,7 +1154,7 @@
         <v/>
       </c>
       <c r="P13">
-        <v>400000</v>
+        <v>108000</v>
       </c>
       <c r="Q13" t="str">
         <v>본사</v>
@@ -1213,7 +1213,7 @@
         <v/>
       </c>
       <c r="P14">
-        <v>400000</v>
+        <v>108000</v>
       </c>
       <c r="Q14" t="str">
         <v/>
@@ -1263,7 +1263,7 @@
         <v>500</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N15" t="str">
         <v>EA</v>
@@ -1272,7 +1272,7 @@
         <v/>
       </c>
       <c r="P15">
-        <v>50000</v>
+        <v>47500</v>
       </c>
       <c r="Q15" t="str">
         <v>본사</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="P16">
-        <v>50000</v>
+        <v>47500</v>
       </c>
       <c r="Q16" t="str">
         <v/>
@@ -1381,7 +1381,7 @@
         <v>5000</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="N17" t="str">
         <v>EA</v>
@@ -1390,7 +1390,7 @@
         <v/>
       </c>
       <c r="P17">
-        <v>500000</v>
+        <v>190000</v>
       </c>
       <c r="Q17" t="str">
         <v>본사</v>
@@ -1449,7 +1449,7 @@
         <v/>
       </c>
       <c r="P18">
-        <v>500000</v>
+        <v>190000</v>
       </c>
       <c r="Q18" t="str">
         <v/>
@@ -1508,7 +1508,7 @@
         <v/>
       </c>
       <c r="P19">
-        <v>1170000</v>
+        <v>926900</v>
       </c>
       <c r="Q19" t="str">
         <v/>
